--- a/test_data/WTA Pillar2 ComplianceCalendar/WTA Pillar2 ComplianceCalendar_Test_Cases.xlsx
+++ b/test_data/WTA Pillar2 ComplianceCalendar/WTA Pillar2 ComplianceCalendar_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>P2Cal_01</t>
+          <t>P2Cal_03</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,43 +522,43 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Compliance Calendar loads with the jurisdiction placeholder</t>
+          <t>The deadline table lists all 5 known deadline types</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>The page must load showing 'Select Jurisdiction' and the left panel instruction text.</t>
+          <t>For Australia the table must include GIR Filing Deadline, Notification Deadline, Registration Deadline, Top-Up Tax Payment Deadline and Top-Up Tax Return Filing Deadline.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>User is logged in.</t>
+          <t>User is logged in, Australia selected on Compliance Calendar.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Country: Australia</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1. Log in and open Pillar 2 &gt; Compliance Calendar
-2. Verify the placeholder text is visible</t>
+          <t>1. Log in, open Compliance Calendar, select Australia
+2. Verify each of the 5 deadline type rows is present</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>The page must load showing 'Select Jurisdiction' and the left panel instruction text.</t>
+          <t>For Australia the table must include GIR Filing Deadline, Notification Deadline, Registration Deadline, Top-Up Tax Payment Deadline and Top-Up Tax Return Filing Deadline.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Compliance Calendar loaded with the jurisdiction placeholder visible.</t>
+          <t>The compliance calendar table for Australia listed all 5 expected deadline types.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>[PASS] Placeholder instruction text is visible</t>
+          <t>[PASS] All 5 deadline type rows are present</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -570,7 +570,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>P2Cal_02</t>
+          <t>P2Cal_04</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -580,164 +580,47 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Selecting a jurisdiction alone renders the deadline table</t>
+          <t>Switching the selected jurisdiction updates the calendar</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Checking 'Australia' (no category needed here) must render a 'Showing compliance calendar of Australia' table.</t>
+          <t>Unchecking Australia and checking Japan instead must update the 'Showing compliance calendar of' text to reference Japan.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and on Compliance Calendar.</t>
+          <t>User is logged in, Australia selected on Compliance Calendar.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Country: Australia</t>
+          <t>Countries: Australia -&gt; Japan</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open Compliance Calendar
-2. Check 'Australia'
-3. Verify the 'Showing compliance calendar of' text and a table are visible</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Checking 'Australia' (no category needed here) must render a 'Showing compliance calendar of Australia' table.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Selecting Australia rendered the compliance calendar table.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Compliance calendar content and table are visible for Australia</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>P2Cal_03</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>WTA Pillar2 ComplianceCalendar</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>The deadline table lists all 5 known deadline types</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>For Australia the table must include GIR Filing Deadline, Notification Deadline, Registration Deadline, Top-Up Tax Payment Deadline and Top-Up Tax Return Filing Deadline.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected on Compliance Calendar.</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Country: Australia</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open Compliance Calendar, select Australia
-2. Verify each of the 5 deadline type rows is present</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>For Australia the table must include GIR Filing Deadline, Notification Deadline, Registration Deadline, Top-Up Tax Payment Deadline and Top-Up Tax Return Filing Deadline.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>The compliance calendar table for Australia listed all 5 expected deadline types.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] All 5 deadline type rows are present</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>P2Cal_04</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>WTA Pillar2 ComplianceCalendar</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Switching the selected jurisdiction updates the calendar</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Unchecking Australia and checking Japan instead must update the 'Showing compliance calendar of' text to reference Japan.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected on Compliance Calendar.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Countries: Australia -&gt; Japan</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Compliance Calendar, select Australia
 2. Uncheck Australia, check Japan
 3. Verify the heading now references Japan</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Unchecking Australia and checking Japan instead must update the 'Showing compliance calendar of' text to reference Japan.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Switching from Australia to Japan updated the compliance calendar to reference Japan.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>[PASS] Calendar content updates to reference Japan after switching jurisdiction</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_data/WTA Pillar2 ComplianceCalendar/WTA Pillar2 ComplianceCalendar_Test_Cases.xlsx
+++ b/test_data/WTA Pillar2 ComplianceCalendar/WTA Pillar2 ComplianceCalendar_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>P2Cal_03</t>
+          <t>P2Cal_01</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,43 +522,43 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>The deadline table lists all 5 known deadline types</t>
+          <t>Compliance Calendar loads with the jurisdiction placeholder</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>For Australia the table must include GIR Filing Deadline, Notification Deadline, Registration Deadline, Top-Up Tax Payment Deadline and Top-Up Tax Return Filing Deadline.</t>
+          <t>The page must load showing 'Select Jurisdiction' and the left panel instruction text.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>User is logged in, Australia selected on Compliance Calendar.</t>
+          <t>User is logged in.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Country: Australia</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1. Log in, open Compliance Calendar, select Australia
-2. Verify each of the 5 deadline type rows is present</t>
+          <t>1. Log in and open Pillar 2 &gt; Compliance Calendar
+2. Verify the placeholder text is visible</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>For Australia the table must include GIR Filing Deadline, Notification Deadline, Registration Deadline, Top-Up Tax Payment Deadline and Top-Up Tax Return Filing Deadline.</t>
+          <t>The page must load showing 'Select Jurisdiction' and the left panel instruction text.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>The compliance calendar table for Australia listed all 5 expected deadline types.</t>
+          <t>Compliance Calendar loaded with the jurisdiction placeholder visible.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>[PASS] All 5 deadline type rows are present</t>
+          <t>[PASS] Placeholder instruction text is visible</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -570,57 +570,174 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>P2Cal_02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>WTA Pillar2 ComplianceCalendar</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Selecting a jurisdiction alone renders the deadline table</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Checking 'Australia' (no category needed here) must render a 'Showing compliance calendar of Australia' table.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on Compliance Calendar.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open Compliance Calendar
+2. Check 'Australia'
+3. Verify the 'Showing compliance calendar of' text and a table are visible</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Checking 'Australia' (no category needed here) must render a 'Showing compliance calendar of Australia' table.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Selecting Australia rendered the compliance calendar table.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Compliance calendar content and table are visible for Australia</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>P2Cal_03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>WTA Pillar2 ComplianceCalendar</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>The deadline table lists all 5 known deadline types</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>For Australia the table must include GIR Filing Deadline, Notification Deadline, Registration Deadline, Top-Up Tax Payment Deadline and Top-Up Tax Return Filing Deadline.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, Australia selected on Compliance Calendar.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open Compliance Calendar, select Australia
+2. Verify each of the 5 deadline type rows is present</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>For Australia the table must include GIR Filing Deadline, Notification Deadline, Registration Deadline, Top-Up Tax Payment Deadline and Top-Up Tax Return Filing Deadline.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>The compliance calendar table for Australia listed all 5 expected deadline types.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] All 5 deadline type rows are present</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
           <t>P2Cal_04</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>WTA Pillar2 ComplianceCalendar</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Switching the selected jurisdiction updates the calendar</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Unchecking Australia and checking Japan instead must update the 'Showing compliance calendar of' text to reference Japan.</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia selected on Compliance Calendar.</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Countries: Australia -&gt; Japan</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Compliance Calendar, select Australia
 2. Uncheck Australia, check Japan
 3. Verify the heading now references Japan</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Unchecking Australia and checking Japan instead must update the 'Showing compliance calendar of' text to reference Japan.</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Switching from Australia to Japan updated the compliance calendar to reference Japan.</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>[PASS] Calendar content updates to reference Japan after switching jurisdiction</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_data/WTA Pillar2 ComplianceCalendar/WTA Pillar2 ComplianceCalendar_Test_Cases.xlsx
+++ b/test_data/WTA Pillar2 ComplianceCalendar/WTA Pillar2 ComplianceCalendar_Test_Cases.xlsx
@@ -44,7 +44,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -553,193 +553,17 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Compliance Calendar loaded with the jurisdiction placeholder visible.</t>
+          <t>Compliance Calendar did not show the expected placeholder.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>[PASS] Placeholder instruction text is visible</t>
+          <t>[FAIL] Placeholder instruction text is visible</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>P2Cal_02</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>WTA Pillar2 ComplianceCalendar</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Selecting a jurisdiction alone renders the deadline table</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Checking 'Australia' (no category needed here) must render a 'Showing compliance calendar of Australia' table.</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on Compliance Calendar.</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Country: Australia</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open Compliance Calendar
-2. Check 'Australia'
-3. Verify the 'Showing compliance calendar of' text and a table are visible</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Checking 'Australia' (no category needed here) must render a 'Showing compliance calendar of Australia' table.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Selecting Australia rendered the compliance calendar table.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Compliance calendar content and table are visible for Australia</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>P2Cal_03</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>WTA Pillar2 ComplianceCalendar</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>The deadline table lists all 5 known deadline types</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>For Australia the table must include GIR Filing Deadline, Notification Deadline, Registration Deadline, Top-Up Tax Payment Deadline and Top-Up Tax Return Filing Deadline.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected on Compliance Calendar.</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Country: Australia</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open Compliance Calendar, select Australia
-2. Verify each of the 5 deadline type rows is present</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>For Australia the table must include GIR Filing Deadline, Notification Deadline, Registration Deadline, Top-Up Tax Payment Deadline and Top-Up Tax Return Filing Deadline.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>The compliance calendar table for Australia listed all 5 expected deadline types.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] All 5 deadline type rows are present</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>P2Cal_04</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>WTA Pillar2 ComplianceCalendar</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Switching the selected jurisdiction updates the calendar</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Unchecking Australia and checking Japan instead must update the 'Showing compliance calendar of' text to reference Japan.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected on Compliance Calendar.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Countries: Australia -&gt; Japan</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open Compliance Calendar, select Australia
-2. Uncheck Australia, check Japan
-3. Verify the heading now references Japan</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Unchecking Australia and checking Japan instead must update the 'Showing compliance calendar of' text to reference Japan.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Switching from Australia to Japan updated the compliance calendar to reference Japan.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Calendar content updates to reference Japan after switching jurisdiction</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
